--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -4,14 +4,14 @@
   <sheets>
     <sheet name="정보" sheetId="1" r:id="rId1"/>
     <sheet name="정간목록" sheetId="2" r:id="rId2"/>
-    <sheet name="악보 1" sheetId="3" r:id="rId3"/>
+    <sheet name="악보" sheetId="3" r:id="rId3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="2">
+  <fonts count="6">
     <font>
       <sz val="11"/>
       <name val="맑은 고딕"/>
@@ -20,6 +20,26 @@
     <font>
       <b/>
       <sz val="11"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="14"/>
+      <name val="맑은 고딕"/>
+    </font>
+    <font>
+      <sz val="22"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="13"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
     </font>
@@ -50,7 +70,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -73,11 +93,71 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFFFFFFF"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFFFFFFF"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="23">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -96,6 +176,54 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2830,8 +2958,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
+  <dimension ref="A1:M18"/>
   <cols>
-    <col min="1" max="1" width="6" customWidth="1"/>
+    <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="9" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
     <col min="4" max="4" width="9" customWidth="1"/>
@@ -2846,656 +2978,660 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="6" t="inlineStr">
-        <is>
-          <t xml:space="preserve">신 만고강산 — 민요채보-2/신 만고강산.png</t>
-        </is>
-      </c>
-      <c r="B1" s="6"/>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
-      <c r="L1" s="6"/>
-      <c r="M1" s="6"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">정간</t>
-        </is>
-      </c>
-      <c r="B2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">6줄</t>
-        </is>
-      </c>
-      <c r="C2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="D2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">5줄</t>
-        </is>
-      </c>
-      <c r="E2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="F2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">4줄</t>
-        </is>
-      </c>
-      <c r="G2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="H2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">3줄</t>
-        </is>
-      </c>
-      <c r="I2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="J2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">2줄</t>
-        </is>
-      </c>
-      <c r="K2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-      <c r="L2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">1줄</t>
-        </is>
-      </c>
-      <c r="M2" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">가사</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="48" customHeight="1">
-      <c r="A3" s="1">
-        <v>1</v>
-      </c>
-      <c r="B3" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">汰
-―
+    <row r="1"/>
+    <row r="2" ht="60" customHeight="1">
+      <c s="8" t="inlineStr" r="B2">
+        <is>
+          <t xml:space="preserve">신 만고강산</t>
+        </is>
+      </c>
+      <c s="8" r="C2"/>
+      <c s="8" r="D2"/>
+      <c s="8" r="E2"/>
+      <c s="8" r="F2"/>
+      <c s="8" r="G2"/>
+      <c s="8" r="H2"/>
+      <c s="8" r="I2"/>
+      <c s="8" r="J2"/>
+      <c s="8" r="K2"/>
+      <c s="8" r="L2"/>
+      <c s="8" r="M2"/>
+    </row>
+    <row r="3" ht="56" customHeight="1">
+      <c r="B3" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">汰
+</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 浹</t>
-        </is>
-      </c>
-      <c r="C3" s="3"/>
-      <c r="D3" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C3" s="17"/>
+      <c r="D3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E3" s="3"/>
-      <c r="F3" s="3" t="inlineStr">
+      <c r="E3" s="17"/>
+      <c r="F3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 潢</t>
         </is>
       </c>
-      <c r="G3" s="3"/>
-      <c r="H3" s="3" t="inlineStr">
+      <c r="G3" s="17"/>
+      <c r="H3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾</t>
         </is>
       </c>
-      <c r="I3" s="3"/>
-      <c r="J3" s="3" t="inlineStr">
+      <c r="I3" s="17"/>
+      <c r="J3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾</t>
         </is>
       </c>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3" t="inlineStr">
+      <c r="K3" s="17"/>
+      <c r="L3" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㳞</t>
         </is>
       </c>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" ht="32" customHeight="1">
-      <c r="A4" s="1">
-        <v>2</v>
-      </c>
-      <c r="B4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C4" s="3"/>
-      <c r="D4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E4" s="3"/>
-      <c r="F4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="M3" s="17"/>
+    </row>
+    <row r="4" ht="56" customHeight="1">
+      <c r="B4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C4" s="18"/>
+      <c r="D4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E4" s="18"/>
+      <c r="F4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 汰</t>
-        </is>
-      </c>
-      <c r="G4" s="3"/>
-      <c r="H4" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+          </r>
+        </is>
+      </c>
+      <c r="G4" s="18"/>
+      <c r="H4" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 無</t>
-        </is>
-      </c>
-      <c r="I4" s="3"/>
-      <c r="J4" s="2"/>
-      <c r="K4" s="2"/>
-      <c r="L4" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="I4" s="18"/>
+      <c r="J4" s="16"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" ht="48" customHeight="1">
-      <c r="A5" s="1">
-        <v>3</v>
-      </c>
-      <c r="B5" s="3" t="inlineStr">
+      <c r="M4" s="18"/>
+    </row>
+    <row r="5" ht="56" customHeight="1">
+      <c r="B5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 浹
 浹</t>
         </is>
       </c>
-      <c r="C5" s="3"/>
-      <c r="D5" s="3" t="inlineStr">
+      <c r="C5" s="18"/>
+      <c r="D5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E5" s="3"/>
-      <c r="F5" s="3" t="inlineStr">
+      <c r="E5" s="18"/>
+      <c r="F5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="G5" s="3"/>
-      <c r="H5" s="3" t="inlineStr">
+      <c r="G5" s="18"/>
+      <c r="H5" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="I5" s="3"/>
-      <c r="J5" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="K5" s="3"/>
-      <c r="L5" s="2"/>
-      <c r="M5" s="2"/>
-    </row>
-    <row r="6" ht="48" customHeight="1">
-      <c r="A6" s="1">
-        <v>4</v>
-      </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="I5" s="18"/>
+      <c r="J5" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="K5" s="18"/>
+      <c r="L5" s="16"/>
+      <c r="M5" s="19"/>
+    </row>
+    <row r="6" ht="56" customHeight="1">
+      <c r="B6" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 浹
 △</t>
         </is>
       </c>
-      <c r="C6" s="3"/>
-      <c r="D6" s="2"/>
-      <c r="E6" s="2"/>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-      <c r="H6" s="2"/>
-      <c r="I6" s="2"/>
-      <c r="J6" s="2"/>
-      <c r="K6" s="2"/>
-      <c r="L6" s="2"/>
-      <c r="M6" s="2"/>
-    </row>
-    <row r="7" ht="48" customHeight="1">
-      <c r="A7" s="1">
-        <v>5</v>
-      </c>
-      <c r="B7" s="3" t="inlineStr">
+      <c r="C6" s="20"/>
+      <c r="D6" s="16"/>
+      <c r="E6" s="21"/>
+      <c r="F6" s="16"/>
+      <c r="G6" s="21"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="21"/>
+      <c r="J6" s="16"/>
+      <c r="K6" s="21"/>
+      <c r="L6" s="16"/>
+      <c r="M6" s="21"/>
+    </row>
+    <row r="7" ht="56" customHeight="1">
+      <c r="B7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 浹</t>
         </is>
       </c>
-      <c r="C7" s="3"/>
-      <c r="D7" s="3" t="inlineStr">
+      <c r="C7" s="17"/>
+      <c r="D7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 黃</t>
         </is>
       </c>
-      <c r="E7" s="3"/>
-      <c r="F7" s="3" t="inlineStr">
+      <c r="E7" s="17"/>
+      <c r="F7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 無</t>
         </is>
       </c>
-      <c r="G7" s="3"/>
-      <c r="H7" s="3" t="inlineStr">
+      <c r="G7" s="17"/>
+      <c r="H7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無
 姑</t>
         </is>
       </c>
-      <c r="I7" s="3"/>
-      <c r="J7" s="3" t="inlineStr">
+      <c r="I7" s="17"/>
+      <c r="J7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3" t="inlineStr">
+      <c r="K7" s="17"/>
+      <c r="L7" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M7" s="3"/>
-    </row>
-    <row r="8" ht="32" customHeight="1">
-      <c r="A8" s="1">
-        <v>6</v>
-      </c>
-      <c r="B8" s="3" t="inlineStr">
+      <c r="M7" s="17"/>
+    </row>
+    <row r="8" ht="56" customHeight="1">
+      <c r="B8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 浹</t>
         </is>
       </c>
-      <c r="C8" s="3"/>
-      <c r="D8" s="2"/>
-      <c r="E8" s="2"/>
-      <c r="F8" s="3" t="inlineStr">
+      <c r="C8" s="18"/>
+      <c r="D8" s="16"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">黃
 姑</t>
         </is>
       </c>
-      <c r="G8" s="3"/>
-      <c r="H8" s="2"/>
-      <c r="I8" s="2"/>
-      <c r="J8" s="2"/>
-      <c r="K8" s="2"/>
-      <c r="L8" s="2"/>
-      <c r="M8" s="2"/>
-    </row>
-    <row r="9" ht="48" customHeight="1">
-      <c r="A9" s="1">
-        <v>7</v>
-      </c>
-      <c r="B9" s="3" t="inlineStr">
+      <c r="G8" s="18"/>
+      <c r="H8" s="16"/>
+      <c r="I8" s="19"/>
+      <c r="J8" s="16"/>
+      <c r="K8" s="19"/>
+      <c r="L8" s="16"/>
+      <c r="M8" s="19"/>
+    </row>
+    <row r="9" ht="56" customHeight="1">
+      <c r="B9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 浹</t>
         </is>
       </c>
-      <c r="C9" s="3"/>
-      <c r="D9" s="3" t="inlineStr">
+      <c r="C9" s="18"/>
+      <c r="D9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 黃</t>
         </is>
       </c>
-      <c r="E9" s="3"/>
-      <c r="F9" s="3" t="inlineStr">
+      <c r="E9" s="18"/>
+      <c r="F9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="G9" s="3"/>
-      <c r="H9" s="3" t="inlineStr">
+      <c r="G9" s="18"/>
+      <c r="H9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰
 南</t>
         </is>
       </c>
-      <c r="I9" s="3"/>
-      <c r="J9" s="3" t="inlineStr">
+      <c r="I9" s="18"/>
+      <c r="J9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3" t="inlineStr">
+      <c r="K9" s="18"/>
+      <c r="L9" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M9" s="3"/>
-    </row>
-    <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="1">
-        <v>8</v>
-      </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="2"/>
-      <c r="E10" s="2"/>
-      <c r="F10" s="3" t="inlineStr">
+      <c r="M9" s="18"/>
+    </row>
+    <row r="10" ht="56" customHeight="1">
+      <c r="B10" s="16"/>
+      <c r="C10" s="21"/>
+      <c r="D10" s="16"/>
+      <c r="E10" s="21"/>
+      <c r="F10" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="G10" s="3"/>
-      <c r="H10" s="2"/>
-      <c r="I10" s="2"/>
-      <c r="J10" s="2"/>
-      <c r="K10" s="2"/>
-      <c r="L10" s="2"/>
-      <c r="M10" s="2"/>
-    </row>
-    <row r="11" ht="32" customHeight="1">
-      <c r="A11" s="1">
-        <v>9</v>
-      </c>
-      <c r="B11" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―
+      <c r="G10" s="20"/>
+      <c r="H10" s="16"/>
+      <c r="I10" s="21"/>
+      <c r="J10" s="16"/>
+      <c r="K10" s="21"/>
+      <c r="L10" s="16"/>
+      <c r="M10" s="21"/>
+    </row>
+    <row r="11" ht="56" customHeight="1">
+      <c r="B11" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+          <r>
+            <rPr>
+              <sz val="22"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">
 浹</t>
-        </is>
-      </c>
-      <c r="C11" s="3"/>
-      <c r="D11" s="3" t="inlineStr">
+          </r>
+        </is>
+      </c>
+      <c r="C11" s="17"/>
+      <c r="D11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E11" s="3"/>
-      <c r="F11" s="3" t="inlineStr">
+      <c r="E11" s="17"/>
+      <c r="F11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G11" s="3"/>
-      <c r="H11" s="3" t="inlineStr">
+      <c r="G11" s="17"/>
+      <c r="H11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="I11" s="3"/>
-      <c r="J11" s="3" t="inlineStr">
+      <c r="I11" s="17"/>
+      <c r="J11" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="K11" s="3"/>
-      <c r="L11" s="2" t="inlineStr">
+      <c r="K11" s="17"/>
+      <c r="L11" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M11" s="2"/>
-    </row>
-    <row r="12" ht="48" customHeight="1">
-      <c r="A12" s="1">
-        <v>10</v>
-      </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="M11" s="22"/>
+    </row>
+    <row r="12" ht="56" customHeight="1">
+      <c r="B12" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">浹
 黃
 無</t>
         </is>
       </c>
-      <c r="C12" s="3"/>
-      <c r="D12" s="2"/>
-      <c r="E12" s="2"/>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-      <c r="H12" s="2"/>
-      <c r="I12" s="2"/>
-      <c r="J12" s="2"/>
-      <c r="K12" s="2"/>
-      <c r="L12" s="2"/>
-      <c r="M12" s="2"/>
-    </row>
-    <row r="13" ht="32" customHeight="1">
-      <c r="A13" s="1">
-        <v>11</v>
-      </c>
-      <c r="B13" s="3" t="inlineStr">
+      <c r="C12" s="18"/>
+      <c r="D12" s="16"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="16"/>
+      <c r="G12" s="19"/>
+      <c r="H12" s="16"/>
+      <c r="I12" s="19"/>
+      <c r="J12" s="16"/>
+      <c r="K12" s="19"/>
+      <c r="L12" s="16"/>
+      <c r="M12" s="19"/>
+    </row>
+    <row r="13" ht="56" customHeight="1">
+      <c r="B13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3" t="inlineStr">
+      <c r="C13" s="18"/>
+      <c r="D13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="E13" s="3"/>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G13" s="2"/>
-      <c r="H13" s="2" t="inlineStr">
+      <c r="E13" s="18"/>
+      <c r="F13" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G13" s="19"/>
+      <c r="H13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I13" s="2"/>
-      <c r="J13" s="3" t="inlineStr">
+      <c r="I13" s="19"/>
+      <c r="J13" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="K13" s="3"/>
-      <c r="L13" s="2" t="inlineStr">
+      <c r="K13" s="18"/>
+      <c r="L13" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">太
 汰</t>
         </is>
       </c>
-      <c r="M13" s="2"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="1">
-        <v>12</v>
-      </c>
-      <c r="B14" s="3" t="inlineStr">
+      <c r="M13" s="19"/>
+    </row>
+    <row r="14" ht="56" customHeight="1">
+      <c r="B14" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="3"/>
-      <c r="D14" s="2"/>
-      <c r="E14" s="2"/>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-      <c r="H14" s="2"/>
-      <c r="I14" s="2"/>
-      <c r="J14" s="2"/>
-      <c r="K14" s="2"/>
-      <c r="L14" s="2"/>
-      <c r="M14" s="2"/>
-    </row>
-    <row r="15" ht="48" customHeight="1">
-      <c r="A15" s="1">
-        <v>13</v>
-      </c>
-      <c r="B15" s="3" t="inlineStr">
+      <c r="C14" s="20"/>
+      <c r="D14" s="16"/>
+      <c r="E14" s="21"/>
+      <c r="F14" s="16"/>
+      <c r="G14" s="21"/>
+      <c r="H14" s="16"/>
+      <c r="I14" s="21"/>
+      <c r="J14" s="16"/>
+      <c r="K14" s="21"/>
+      <c r="L14" s="16"/>
+      <c r="M14" s="21"/>
+    </row>
+    <row r="15" ht="56" customHeight="1">
+      <c r="B15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 浹</t>
         </is>
       </c>
-      <c r="C15" s="3"/>
-      <c r="D15" s="3" t="inlineStr">
+      <c r="C15" s="17"/>
+      <c r="D15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 黃</t>
         </is>
       </c>
-      <c r="E15" s="3"/>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="G15" s="2"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="I15" s="2"/>
-      <c r="J15" s="3" t="inlineStr">
+      <c r="E15" s="17"/>
+      <c r="F15" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="G15" s="22"/>
+      <c r="H15" s="16" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="I15" s="22"/>
+      <c r="J15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 汰
 夾</t>
         </is>
       </c>
-      <c r="K15" s="3"/>
-      <c r="L15" s="3" t="inlineStr">
+      <c r="K15" s="17"/>
+      <c r="L15" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M15" s="3"/>
-    </row>
-    <row r="16" ht="32" customHeight="1">
-      <c r="A16" s="1">
-        <v>14</v>
-      </c>
-      <c r="B16" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C16" s="3"/>
-      <c r="D16" s="2"/>
-      <c r="E16" s="2"/>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-      <c r="H16" s="2" t="inlineStr">
+      <c r="M15" s="17"/>
+    </row>
+    <row r="16" ht="56" customHeight="1">
+      <c r="B16" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C16" s="18"/>
+      <c r="D16" s="16"/>
+      <c r="E16" s="19"/>
+      <c r="F16" s="16"/>
+      <c r="G16" s="19"/>
+      <c r="H16" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I16" s="2"/>
-      <c r="J16" s="2"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="2"/>
-      <c r="M16" s="2"/>
-    </row>
-    <row r="17" ht="32" customHeight="1">
-      <c r="A17" s="1">
-        <v>15</v>
-      </c>
-      <c r="B17" s="3" t="inlineStr">
+      <c r="I16" s="19"/>
+      <c r="J16" s="16"/>
+      <c r="K16" s="19"/>
+      <c r="L16" s="16"/>
+      <c r="M16" s="19"/>
+    </row>
+    <row r="17" ht="56" customHeight="1">
+      <c r="B17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="C17" s="3"/>
-      <c r="D17" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="E17" s="3"/>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-      <c r="H17" s="3" t="inlineStr">
+      <c r="C17" s="18"/>
+      <c r="D17" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="E17" s="18"/>
+      <c r="F17" s="16"/>
+      <c r="G17" s="19"/>
+      <c r="H17" s="15" t="inlineStr">
         <is>
           <t xml:space="preserve">夾
 黃</t>
         </is>
       </c>
-      <c r="I17" s="3"/>
-      <c r="J17" s="2" t="inlineStr">
+      <c r="I17" s="18"/>
+      <c r="J17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 黃</t>
         </is>
       </c>
-      <c r="K17" s="2"/>
-      <c r="L17" s="2" t="inlineStr">
+      <c r="K17" s="19"/>
+      <c r="L17" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M17" s="2"/>
-    </row>
-    <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="1">
-        <v>16</v>
-      </c>
-      <c r="B18" s="3" t="inlineStr">
-        <is>
-          <t xml:space="preserve">―</t>
-        </is>
-      </c>
-      <c r="C18" s="3"/>
-      <c r="D18" s="2"/>
-      <c r="E18" s="2"/>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-      <c r="H18" s="2" t="inlineStr">
+      <c r="M17" s="19"/>
+    </row>
+    <row r="18" ht="56" customHeight="1">
+      <c r="B18" s="15" t="inlineStr">
+        <is>
+          <r>
+            <rPr>
+              <sz val="11"/>
+              <rFont val="맑은 고딕"/>
+            </rPr>
+            <t xml:space="preserve">―</t>
+          </r>
+        </is>
+      </c>
+      <c r="C18" s="20"/>
+      <c r="D18" s="16"/>
+      <c r="E18" s="21"/>
+      <c r="F18" s="16"/>
+      <c r="G18" s="21"/>
+      <c r="H18" s="16" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="I18" s="2"/>
-      <c r="J18" s="2"/>
-      <c r="K18" s="2"/>
-      <c r="L18" s="2"/>
-      <c r="M18" s="2"/>
+      <c r="I18" s="21"/>
+      <c r="J18" s="16"/>
+      <c r="K18" s="21"/>
+      <c r="L18" s="16"/>
+      <c r="M18" s="21"/>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="B2:M2"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" fitToWidth="1" fitToHeight="0" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -409,7 +409,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">― 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
+          <t xml:space="preserve">– 연음 · △ 쉼 · 점 · ○ 동그라미 · ⁚ 두 점 · ‹ 정간 경계 표시 · ／ 사선 (· ○ ⁚ ‹ ／ 는 화면 표시 전용)</t>
         </is>
       </c>
     </row>
@@ -837,13 +837,13 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―</t>
+          <t xml:space="preserve">汰|–</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I10" s="2"/>
@@ -1050,13 +1050,13 @@
       </c>
       <c r="G16" s="3" t="inlineStr">
         <is>
-          <t xml:space="preserve">汰|―</t>
+          <t xml:space="preserve">汰|–</t>
         </is>
       </c>
       <c r="H16" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="I16" s="3"/>
@@ -1129,13 +1129,13 @@
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I18" s="2"/>
@@ -1344,13 +1344,13 @@
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I24" s="2"/>
@@ -1592,13 +1592,13 @@
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">黃無|―</t>
+          <t xml:space="preserve">黃無|–</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
-―</t>
+–</t>
         </is>
       </c>
       <c r="I31" s="2"/>
@@ -1807,12 +1807,12 @@
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I37" s="2"/>
@@ -1842,13 +1842,13 @@
       </c>
       <c r="G38" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I38" s="2"/>
@@ -1950,12 +1950,12 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I41" s="2"/>
@@ -2270,13 +2270,13 @@
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑潕|―</t>
+          <t xml:space="preserve">姑潕|–</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潕
-―</t>
+–</t>
         </is>
       </c>
       <c r="I50" s="2"/>
@@ -2342,12 +2342,12 @@
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I52" s="2"/>
@@ -2413,12 +2413,12 @@
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I54" s="2"/>
@@ -2519,13 +2519,13 @@
       </c>
       <c r="G57" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I57" s="2"/>
@@ -2805,13 +2805,13 @@
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢|―</t>
+          <t xml:space="preserve">潢|–</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="I65" s="2"/>
@@ -2912,12 +2912,12 @@
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I68" s="2"/>
@@ -3123,12 +3123,12 @@
       </c>
       <c r="G74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I74" s="2"/>
@@ -3228,13 +3228,13 @@
       </c>
       <c r="G77" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑|―</t>
+          <t xml:space="preserve">姑姑|–</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I77" s="2"/>
@@ -3412,12 +3412,12 @@
       </c>
       <c r="G82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I82" s="2"/>
@@ -3482,12 +3482,12 @@
       </c>
       <c r="G84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I84" s="2"/>
@@ -3517,13 +3517,13 @@
       </c>
       <c r="G85" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|―</t>
+          <t xml:space="preserve">姑|–</t>
         </is>
       </c>
       <c r="H85" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I85" s="2"/>
@@ -3763,12 +3763,12 @@
       </c>
       <c r="G92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I92" s="2"/>
@@ -3852,7 +3852,7 @@
       <c r="J3" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K3" s="8"/>
@@ -3914,14 +3914,14 @@
       <c r="D5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="E5" s="9"/>
       <c r="F5" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潕
-―</t>
+–</t>
         </is>
       </c>
       <c r="G5" s="9"/>
@@ -3950,7 +3950,7 @@
       <c r="A6" s="0"/>
       <c r="B6" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C6" s="10"/>
@@ -4024,25 +4024,25 @@
       <c r="A8" s="0"/>
       <c r="B8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C8" s="9"/>
       <c r="D8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E8" s="9"/>
       <c r="F8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G8" s="9"/>
       <c r="H8" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I8" s="9"/>
@@ -4064,7 +4064,7 @@
       <c r="B9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="C9" s="9"/>
@@ -4084,14 +4084,14 @@
       <c r="H9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="I9" s="9"/>
       <c r="J9" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="K9" s="9"/>
@@ -4120,7 +4120,7 @@
       <c r="E10" s="10"/>
       <c r="F10" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="G10" s="10"/>
@@ -4181,7 +4181,7 @@
       <c r="L11" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="M11" s="8"/>
@@ -4208,7 +4208,7 @@
       <c r="G12" s="9"/>
       <c r="H12" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I12" s="9"/>
@@ -4242,7 +4242,7 @@
       <c r="F13" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
-―</t>
+–</t>
         </is>
       </c>
       <c r="G13" s="9"/>
@@ -4277,7 +4277,7 @@
       <c r="C14" s="10"/>
       <c r="D14" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E14" s="10"/>
@@ -4347,7 +4347,7 @@
       <c r="A16" s="0"/>
       <c r="B16" s="17" t="inlineStr">
         <is>
-          <t xml:space="preserve">―</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C16" s="9"/>
@@ -4389,7 +4389,7 @@
       <c r="D17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
-―</t>
+–</t>
         </is>
       </c>
       <c r="E17" s="9"/>
@@ -4408,14 +4408,14 @@
       <c r="J17" s="17" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
-―</t>
+–</t>
         </is>
       </c>
       <c r="K17" s="9"/>
       <c r="L17" s="18" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
-―</t>
+–</t>
         </is>
       </c>
       <c r="M17" s="12"/>

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -11,27 +11,43 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="4">
+  <fonts count="7">
     <font>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="14"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
     <font>
       <sz val="22"/>
-      <name val="맑은 고딕"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="24"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <name val="궁서체"/>
       <family val="2"/>
     </font>
   </fonts>
@@ -134,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="20">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -157,7 +173,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <!-- 8~16: 박 묶음 가사 칸 = (일반 8~10 · 비고 11~13 · 팔레트 외 14~16) × (첫 · 가운데 · 마지막) -->
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -185,7 +200,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <!-- 17~19: 악보 율명 칸 22pt (가사 11pt 의 두 배) = 일반 · 비고 · 팔레트 외 -->
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -193,6 +207,33 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -3803,658 +3844,658 @@
     </row>
     <row r="2" ht="60" customHeight="1">
       <c r="A2" s="0"/>
-      <c r="B2" s="7" t="inlineStr">
+      <c r="B2" s="20" t="inlineStr">
         <is>
           <t xml:space="preserve">신 만고강산</t>
         </is>
       </c>
-      <c r="C2" s="7"/>
-      <c r="D2" s="7"/>
-      <c r="E2" s="7"/>
-      <c r="F2" s="7"/>
-      <c r="G2" s="7"/>
-      <c r="H2" s="7"/>
-      <c r="I2" s="7"/>
-      <c r="J2" s="7"/>
-      <c r="K2" s="7"/>
-      <c r="L2" s="7"/>
-      <c r="M2" s="7"/>
+      <c r="C2" s="20"/>
+      <c r="D2" s="20"/>
+      <c r="E2" s="20"/>
+      <c r="F2" s="20"/>
+      <c r="G2" s="20"/>
+      <c r="H2" s="20"/>
+      <c r="I2" s="20"/>
+      <c r="J2" s="20"/>
+      <c r="K2" s="20"/>
+      <c r="L2" s="20"/>
+      <c r="M2" s="20"/>
     </row>
     <row r="3" ht="56" customHeight="1">
       <c r="A3" s="0"/>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃潢</t>
         </is>
       </c>
-      <c r="C3" s="11"/>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="C3" s="22"/>
+      <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="11"/>
-      <c r="F3" s="18" t="inlineStr">
+      <c r="E3" s="22"/>
+      <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G3" s="11"/>
-      <c r="H3" s="17" t="inlineStr">
+      <c r="G3" s="22"/>
+      <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I3" s="8"/>
-      <c r="J3" s="17" t="inlineStr">
+      <c r="I3" s="24"/>
+      <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K3" s="8"/>
-      <c r="L3" s="17" t="inlineStr">
+      <c r="K3" s="24"/>
+      <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="M3" s="8"/>
+      <c r="M3" s="24"/>
     </row>
     <row r="4" ht="56" customHeight="1">
       <c r="A4" s="0"/>
-      <c r="B4" s="17" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="17" t="inlineStr">
+      <c r="C4" s="25"/>
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="17" t="inlineStr">
+      <c r="E4" s="25"/>
+      <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="17" t="inlineStr">
+      <c r="G4" s="25"/>
+      <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="17" t="inlineStr">
+      <c r="I4" s="25"/>
+      <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="17" t="inlineStr">
+      <c r="K4" s="25"/>
+      <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="9"/>
+      <c r="M4" s="25"/>
     </row>
     <row r="5" ht="56" customHeight="1">
       <c r="A5" s="0"/>
-      <c r="B5" s="18" t="inlineStr">
+      <c r="B5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潕潢潕</t>
         </is>
       </c>
-      <c r="C5" s="12"/>
-      <c r="D5" s="17" t="inlineStr">
+      <c r="C5" s="26"/>
+      <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="17" t="inlineStr">
+      <c r="E5" s="25"/>
+      <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潕
 –</t>
         </is>
       </c>
-      <c r="G5" s="9"/>
-      <c r="H5" s="17" t="inlineStr">
+      <c r="G5" s="25"/>
+      <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="I5" s="9"/>
-      <c r="J5" s="18" t="inlineStr">
+      <c r="I5" s="25"/>
+      <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無</t>
         </is>
       </c>
-      <c r="K5" s="12"/>
-      <c r="L5" s="17" t="inlineStr">
+      <c r="K5" s="26"/>
+      <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌</t>
         </is>
       </c>
-      <c r="M5" s="9"/>
+      <c r="M5" s="25"/>
     </row>
     <row r="6" ht="56" customHeight="1">
       <c r="A6" s="0"/>
-      <c r="B6" s="17" t="inlineStr">
+      <c r="B6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="10"/>
-      <c r="D6" s="17" t="inlineStr">
+      <c r="C6" s="27"/>
+      <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢
 ○</t>
         </is>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="17"/>
-      <c r="G6" s="10"/>
-      <c r="H6" s="17"/>
-      <c r="I6" s="10"/>
-      <c r="J6" s="17" t="inlineStr">
+      <c r="E6" s="27"/>
+      <c r="F6" s="23"/>
+      <c r="G6" s="27"/>
+      <c r="H6" s="23"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑無</t>
         </is>
       </c>
-      <c r="K6" s="10"/>
-      <c r="L6" s="17" t="inlineStr">
+      <c r="K6" s="27"/>
+      <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M6" s="10"/>
+      <c r="M6" s="27"/>
     </row>
     <row r="7" ht="56" customHeight="1">
       <c r="A7" s="0"/>
-      <c r="B7" s="17" t="inlineStr">
+      <c r="B7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="C7" s="8"/>
-      <c r="D7" s="17" t="inlineStr">
+      <c r="C7" s="24"/>
+      <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E7" s="8"/>
-      <c r="F7" s="17" t="inlineStr">
+      <c r="E7" s="24"/>
+      <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="G7" s="8"/>
-      <c r="H7" s="17" t="inlineStr">
+      <c r="G7" s="24"/>
+      <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 湳</t>
         </is>
       </c>
-      <c r="I7" s="8"/>
-      <c r="J7" s="17" t="inlineStr">
+      <c r="I7" s="24"/>
+      <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃姑無</t>
         </is>
       </c>
-      <c r="K7" s="8"/>
-      <c r="L7" s="17" t="inlineStr">
+      <c r="K7" s="24"/>
+      <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="M7" s="8"/>
+      <c r="M7" s="24"/>
     </row>
     <row r="8" ht="56" customHeight="1">
       <c r="A8" s="0"/>
-      <c r="B8" s="17" t="inlineStr">
+      <c r="B8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="9"/>
-      <c r="D8" s="17" t="inlineStr">
+      <c r="C8" s="25"/>
+      <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="9"/>
-      <c r="F8" s="17" t="inlineStr">
+      <c r="E8" s="25"/>
+      <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="9"/>
-      <c r="H8" s="17" t="inlineStr">
+      <c r="G8" s="25"/>
+      <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="9"/>
-      <c r="J8" s="17" t="inlineStr">
+      <c r="I8" s="25"/>
+      <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="9"/>
-      <c r="L8" s="17" t="inlineStr">
+      <c r="K8" s="25"/>
+      <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M8" s="9"/>
+      <c r="M8" s="25"/>
     </row>
     <row r="9" ht="56" customHeight="1">
       <c r="A9" s="0"/>
-      <c r="B9" s="17" t="inlineStr">
+      <c r="B9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="C9" s="9"/>
-      <c r="D9" s="17" t="inlineStr">
+      <c r="C9" s="25"/>
+      <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E9" s="9"/>
-      <c r="F9" s="17" t="inlineStr">
+      <c r="E9" s="25"/>
+      <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G9" s="9"/>
-      <c r="H9" s="17" t="inlineStr">
+      <c r="G9" s="25"/>
+      <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I9" s="9"/>
-      <c r="J9" s="17" t="inlineStr">
+      <c r="I9" s="25"/>
+      <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K9" s="9"/>
-      <c r="L9" s="18" t="inlineStr">
+      <c r="K9" s="25"/>
+      <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="M9" s="12"/>
+      <c r="M9" s="26"/>
     </row>
     <row r="10" ht="56" customHeight="1">
       <c r="A10" s="0"/>
-      <c r="B10" s="17" t="inlineStr">
+      <c r="B10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="17" t="inlineStr">
+      <c r="C10" s="27"/>
+      <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="17" t="inlineStr">
+      <c r="E10" s="27"/>
+      <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="10"/>
-      <c r="H10" s="17" t="inlineStr">
+      <c r="G10" s="27"/>
+      <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="I10" s="10"/>
-      <c r="J10" s="17" t="inlineStr">
+      <c r="I10" s="27"/>
+      <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="K10" s="10"/>
-      <c r="L10" s="17" t="inlineStr">
+      <c r="K10" s="27"/>
+      <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M10" s="10"/>
+      <c r="M10" s="27"/>
     </row>
     <row r="11" ht="56" customHeight="1">
       <c r="A11" s="0"/>
-      <c r="B11" s="17" t="inlineStr">
+      <c r="B11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="8"/>
-      <c r="D11" s="17" t="inlineStr">
+      <c r="C11" s="24"/>
+      <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E11" s="8"/>
-      <c r="F11" s="17" t="inlineStr">
+      <c r="E11" s="24"/>
+      <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G11" s="8"/>
-      <c r="H11" s="17" t="inlineStr">
+      <c r="G11" s="24"/>
+      <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
 潢</t>
         </is>
       </c>
-      <c r="I11" s="8"/>
-      <c r="J11" s="17" t="inlineStr">
+      <c r="I11" s="24"/>
+      <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K11" s="8"/>
-      <c r="L11" s="17" t="inlineStr">
+      <c r="K11" s="24"/>
+      <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="M11" s="8"/>
+      <c r="M11" s="24"/>
     </row>
     <row r="12" ht="56" customHeight="1">
       <c r="A12" s="0"/>
-      <c r="B12" s="17" t="inlineStr">
+      <c r="B12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C12" s="9"/>
-      <c r="D12" s="17" t="inlineStr">
+      <c r="C12" s="25"/>
+      <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E12" s="9"/>
-      <c r="F12" s="17" t="inlineStr">
+      <c r="E12" s="25"/>
+      <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="9"/>
-      <c r="H12" s="17" t="inlineStr">
+      <c r="G12" s="25"/>
+      <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="9"/>
-      <c r="J12" s="17" t="inlineStr">
+      <c r="I12" s="25"/>
+      <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="K12" s="9"/>
-      <c r="L12" s="17" t="inlineStr">
+      <c r="K12" s="25"/>
+      <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M12" s="9"/>
+      <c r="M12" s="25"/>
     </row>
     <row r="13" ht="56" customHeight="1">
       <c r="A13" s="0"/>
-      <c r="B13" s="17" t="inlineStr">
+      <c r="B13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="C13" s="9"/>
-      <c r="D13" s="17" t="inlineStr">
+      <c r="C13" s="25"/>
+      <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E13" s="9"/>
-      <c r="F13" s="17" t="inlineStr">
+      <c r="E13" s="25"/>
+      <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="G13" s="9"/>
-      <c r="H13" s="17" t="inlineStr">
+      <c r="G13" s="25"/>
+      <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I13" s="9"/>
-      <c r="J13" s="17" t="inlineStr">
+      <c r="I13" s="25"/>
+      <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K13" s="9"/>
-      <c r="L13" s="17" t="inlineStr">
+      <c r="K13" s="25"/>
+      <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M13" s="9"/>
+      <c r="M13" s="25"/>
     </row>
     <row r="14" ht="56" customHeight="1">
       <c r="A14" s="0"/>
-      <c r="B14" s="17" t="inlineStr">
+      <c r="B14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="10"/>
-      <c r="D14" s="17" t="inlineStr">
+      <c r="C14" s="27"/>
+      <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="10"/>
-      <c r="F14" s="17" t="inlineStr">
+      <c r="E14" s="27"/>
+      <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G14" s="10"/>
-      <c r="H14" s="17" t="inlineStr">
+      <c r="G14" s="27"/>
+      <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I14" s="10"/>
-      <c r="J14" s="17"/>
-      <c r="K14" s="10"/>
-      <c r="L14" s="17" t="inlineStr">
+      <c r="I14" s="27"/>
+      <c r="J14" s="23"/>
+      <c r="K14" s="27"/>
+      <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M14" s="10"/>
+      <c r="M14" s="27"/>
     </row>
     <row r="15" ht="56" customHeight="1">
       <c r="A15" s="0"/>
-      <c r="B15" s="17" t="inlineStr">
+      <c r="B15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C15" s="8"/>
-      <c r="D15" s="17" t="inlineStr">
+      <c r="C15" s="24"/>
+      <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E15" s="8"/>
-      <c r="F15" s="17" t="inlineStr">
+      <c r="E15" s="24"/>
+      <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="G15" s="8"/>
-      <c r="H15" s="17" t="inlineStr">
+      <c r="G15" s="24"/>
+      <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I15" s="8"/>
-      <c r="J15" s="17" t="inlineStr">
+      <c r="I15" s="24"/>
+      <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
 湳</t>
         </is>
       </c>
-      <c r="K15" s="8"/>
-      <c r="L15" s="17" t="inlineStr">
+      <c r="K15" s="24"/>
+      <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="M15" s="8"/>
+      <c r="M15" s="24"/>
     </row>
     <row r="16" ht="56" customHeight="1">
       <c r="A16" s="0"/>
-      <c r="B16" s="17" t="inlineStr">
+      <c r="B16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="9"/>
-      <c r="D16" s="17" t="inlineStr">
+      <c r="C16" s="25"/>
+      <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E16" s="9"/>
-      <c r="F16" s="17" t="inlineStr">
+      <c r="E16" s="25"/>
+      <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G16" s="9"/>
-      <c r="H16" s="17" t="inlineStr">
+      <c r="G16" s="25"/>
+      <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I16" s="9"/>
-      <c r="J16" s="17" t="inlineStr">
+      <c r="I16" s="25"/>
+      <c r="J16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K16" s="9"/>
-      <c r="L16" s="17" t="inlineStr">
+      <c r="K16" s="25"/>
+      <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M16" s="9"/>
+      <c r="M16" s="25"/>
     </row>
     <row r="17" ht="56" customHeight="1">
       <c r="A17" s="0"/>
-      <c r="B17" s="17"/>
-      <c r="C17" s="9"/>
-      <c r="D17" s="17" t="inlineStr">
+      <c r="B17" s="23"/>
+      <c r="C17" s="25"/>
+      <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
 –</t>
         </is>
       </c>
-      <c r="E17" s="9"/>
-      <c r="F17" s="17" t="inlineStr">
+      <c r="E17" s="25"/>
+      <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="G17" s="9"/>
-      <c r="H17" s="17" t="inlineStr">
+      <c r="G17" s="25"/>
+      <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="9"/>
-      <c r="J17" s="17" t="inlineStr">
+      <c r="I17" s="25"/>
+      <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
 –</t>
         </is>
       </c>
-      <c r="K17" s="9"/>
-      <c r="L17" s="18" t="inlineStr">
+      <c r="K17" s="25"/>
+      <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="M17" s="12"/>
+      <c r="M17" s="26"/>
     </row>
     <row r="18" ht="56" customHeight="1">
       <c r="A18" s="0"/>
-      <c r="B18" s="17"/>
-      <c r="C18" s="10"/>
-      <c r="D18" s="17" t="inlineStr">
+      <c r="B18" s="23"/>
+      <c r="C18" s="27"/>
+      <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="17" t="inlineStr">
+      <c r="E18" s="27"/>
+      <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G18" s="10"/>
-      <c r="H18" s="17" t="inlineStr">
+      <c r="G18" s="27"/>
+      <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·</t>
         </is>
       </c>
-      <c r="I18" s="10"/>
-      <c r="J18" s="17" t="inlineStr">
+      <c r="I18" s="27"/>
+      <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">·
 ○</t>
         </is>
       </c>
-      <c r="K18" s="10"/>
-      <c r="L18" s="18" t="inlineStr">
+      <c r="K18" s="27"/>
+      <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="13"/>
+      <c r="M18" s="28"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -3825,24 +3825,24 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="9" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="9" customWidth="1"/>
+    <col min="4" max="4" width="12" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="9" customWidth="1"/>
+    <col min="6" max="6" width="12" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="9" customWidth="1"/>
+    <col min="8" max="8" width="12" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="9" customWidth="1"/>
+    <col min="10" max="10" width="12" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="9" customWidth="1"/>
+    <col min="12" max="12" width="12" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="60" customHeight="1">
+    <row r="2" ht="55.19" customHeight="1">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -3861,7 +3861,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="56" customHeight="1">
+    <row r="3" ht="55.19" customHeight="1">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -3905,7 +3905,7 @@
       </c>
       <c r="M3" s="24"/>
     </row>
-    <row r="4" ht="56" customHeight="1">
+    <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -3944,7 +3944,7 @@
       </c>
       <c r="M4" s="25"/>
     </row>
-    <row r="5" ht="56" customHeight="1">
+    <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -3987,7 +3987,7 @@
       </c>
       <c r="M5" s="25"/>
     </row>
-    <row r="6" ht="56" customHeight="1">
+    <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
       <c r="B6" s="23" t="inlineStr">
         <is>
@@ -4019,7 +4019,7 @@
       </c>
       <c r="M6" s="27"/>
     </row>
-    <row r="7" ht="56" customHeight="1">
+    <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
       <c r="B7" s="23" t="inlineStr">
         <is>
@@ -4061,7 +4061,7 @@
       </c>
       <c r="M7" s="24"/>
     </row>
-    <row r="8" ht="56" customHeight="1">
+    <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
       <c r="B8" s="23" t="inlineStr">
         <is>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="M8" s="25"/>
     </row>
-    <row r="9" ht="56" customHeight="1">
+    <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
       <c r="B9" s="23" t="inlineStr">
         <is>
@@ -4144,17 +4144,17 @@
       </c>
       <c r="M9" s="26"/>
     </row>
-    <row r="10" ht="56" customHeight="1">
+    <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
       <c r="B10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="C10" s="27"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
@@ -4167,14 +4167,14 @@
       <c r="G10" s="27"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>
       <c r="I10" s="27"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K10" s="27"/>
@@ -4185,7 +4185,7 @@
       </c>
       <c r="M10" s="27"/>
     </row>
-    <row r="11" ht="56" customHeight="1">
+    <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
       <c r="B11" s="23" t="inlineStr">
         <is>
@@ -4227,7 +4227,7 @@
       </c>
       <c r="M11" s="24"/>
     </row>
-    <row r="12" ht="56" customHeight="1">
+    <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
       <c r="B12" s="23" t="inlineStr">
         <is>
@@ -4266,7 +4266,7 @@
       </c>
       <c r="M12" s="25"/>
     </row>
-    <row r="13" ht="56" customHeight="1">
+    <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
       <c r="B13" s="23" t="inlineStr">
         <is>
@@ -4289,7 +4289,7 @@
       <c r="G13" s="25"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I13" s="25"/>
@@ -4308,7 +4308,7 @@
       </c>
       <c r="M13" s="25"/>
     </row>
-    <row r="14" ht="56" customHeight="1">
+    <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
       <c r="B14" s="23" t="inlineStr">
         <is>
@@ -4330,7 +4330,7 @@
       <c r="G14" s="27"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I14" s="27"/>
@@ -4343,7 +4343,7 @@
       </c>
       <c r="M14" s="27"/>
     </row>
-    <row r="15" ht="56" customHeight="1">
+    <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
       <c r="B15" s="23" t="inlineStr">
         <is>
@@ -4365,7 +4365,7 @@
       <c r="G15" s="24"/>
       <c r="H15" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I15" s="24"/>
@@ -4384,7 +4384,7 @@
       </c>
       <c r="M15" s="24"/>
     </row>
-    <row r="16" ht="56" customHeight="1">
+    <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
       <c r="B16" s="23" t="inlineStr">
         <is>
@@ -4406,7 +4406,7 @@
       <c r="G16" s="25"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I16" s="25"/>
@@ -4423,7 +4423,7 @@
       </c>
       <c r="M16" s="25"/>
     </row>
-    <row r="17" ht="56" customHeight="1">
+    <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
       <c r="C17" s="25"/>
@@ -4461,7 +4461,7 @@
       </c>
       <c r="M17" s="26"/>
     </row>
-    <row r="18" ht="56" customHeight="1">
+    <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
       <c r="C18" s="27"/>
@@ -4479,13 +4479,13 @@
       <c r="G18" s="27"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I18" s="27"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
+          <t xml:space="preserve">–
 ○</t>
         </is>
       </c>

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -1669,13 +1669,12 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I32" s="2"/>
@@ -1919,13 +1918,12 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I39" s="2"/>
@@ -2882,13 +2880,12 @@
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢|○</t>
+          <t xml:space="preserve">淋潢</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢
-○</t>
+          <t xml:space="preserve">淋潢</t>
         </is>
       </c>
       <c r="I66" s="2"/>
@@ -3023,13 +3020,12 @@
       </c>
       <c r="G70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·|○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">·
-○</t>
+          <t xml:space="preserve">·</t>
         </is>
       </c>
       <c r="I70" s="2"/>
@@ -3997,8 +3993,7 @@
       <c r="C6" s="27"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">淋潢
-○</t>
+          <t xml:space="preserve">淋潢</t>
         </is>
       </c>
       <c r="E6" s="27"/>
@@ -4154,8 +4149,7 @@
       <c r="C10" s="27"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="E10" s="27"/>
@@ -4167,8 +4161,7 @@
       <c r="G10" s="27"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="I10" s="27"/>
@@ -4485,8 +4478,7 @@
       <c r="I18" s="27"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
-          <t xml:space="preserve">–
-○</t>
+          <t xml:space="preserve">–</t>
         </is>
       </c>
       <c r="K18" s="27"/>

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -11,7 +11,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="7">
+  <fonts count="8">
     <font>
       <sz val="11"/>
       <name val="궁서체"/>
@@ -47,6 +47,11 @@
     </font>
     <font>
       <sz val="12"/>
+      <name val="궁서체"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="18"/>
       <name val="궁서체"/>
       <family val="2"/>
     </font>
@@ -150,7 +155,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="29">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -236,6 +241,24 @@
     <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -3864,42 +3887,42 @@
           <t xml:space="preserve">黃潢</t>
         </is>
       </c>
-      <c r="C3" s="22"/>
+      <c r="C3" s="29"/>
       <c r="D3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="E3" s="22"/>
+      <c r="E3" s="29"/>
       <c r="F3" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 潢</t>
         </is>
       </c>
-      <c r="G3" s="22"/>
+      <c r="G3" s="29"/>
       <c r="H3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 潢</t>
         </is>
       </c>
-      <c r="I3" s="24"/>
+      <c r="I3" s="30"/>
       <c r="J3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K3" s="24"/>
+      <c r="K3" s="30"/>
       <c r="L3" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="M3" s="24"/>
+      <c r="M3" s="30"/>
     </row>
     <row r="4" ht="55.19" customHeight="1">
       <c r="A4" s="0"/>
@@ -3908,37 +3931,37 @@
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="C4" s="25"/>
+      <c r="C4" s="31"/>
       <c r="D4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潕</t>
         </is>
       </c>
-      <c r="E4" s="25"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G4" s="25"/>
+      <c r="G4" s="31"/>
       <c r="H4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="I4" s="25"/>
+      <c r="I4" s="31"/>
       <c r="J4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="K4" s="25"/>
+      <c r="K4" s="31"/>
       <c r="L4" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="M4" s="25"/>
+      <c r="M4" s="31"/>
     </row>
     <row r="5" ht="55.19" customHeight="1">
       <c r="A5" s="0"/>
@@ -3947,41 +3970,41 @@
           <t xml:space="preserve">潕潢潕</t>
         </is>
       </c>
-      <c r="C5" s="26"/>
+      <c r="C5" s="32"/>
       <c r="D5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="E5" s="25"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑潕
 –</t>
         </is>
       </c>
-      <c r="G5" s="25"/>
+      <c r="G5" s="31"/>
       <c r="H5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="I5" s="25"/>
+      <c r="I5" s="31"/>
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無</t>
         </is>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="32"/>
       <c r="L5" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 㴌</t>
         </is>
       </c>
-      <c r="M5" s="25"/>
+      <c r="M5" s="31"/>
     </row>
     <row r="6" ht="55.19" customHeight="1">
       <c r="A6" s="0"/>
@@ -3990,29 +4013,29 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C6" s="27"/>
+      <c r="C6" s="33"/>
       <c r="D6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">淋潢</t>
         </is>
       </c>
-      <c r="E6" s="27"/>
+      <c r="E6" s="33"/>
       <c r="F6" s="23"/>
-      <c r="G6" s="27"/>
+      <c r="G6" s="33"/>
       <c r="H6" s="23"/>
-      <c r="I6" s="27"/>
+      <c r="I6" s="33"/>
       <c r="J6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南姑無</t>
         </is>
       </c>
-      <c r="K6" s="27"/>
+      <c r="K6" s="33"/>
       <c r="L6" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M6" s="27"/>
+      <c r="M6" s="33"/>
     </row>
     <row r="7" ht="55.19" customHeight="1">
       <c r="A7" s="0"/>
@@ -4021,40 +4044,40 @@
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="C7" s="24"/>
+      <c r="C7" s="30"/>
       <c r="D7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E7" s="24"/>
+      <c r="E7" s="30"/>
       <c r="F7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 △</t>
         </is>
       </c>
-      <c r="G7" s="24"/>
+      <c r="G7" s="30"/>
       <c r="H7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 湳</t>
         </is>
       </c>
-      <c r="I7" s="24"/>
+      <c r="I7" s="30"/>
       <c r="J7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃姑無</t>
         </is>
       </c>
-      <c r="K7" s="24"/>
+      <c r="K7" s="30"/>
       <c r="L7" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 㴌</t>
         </is>
       </c>
-      <c r="M7" s="24"/>
+      <c r="M7" s="30"/>
     </row>
     <row r="8" ht="55.19" customHeight="1">
       <c r="A8" s="0"/>
@@ -4063,37 +4086,37 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C8" s="25"/>
+      <c r="C8" s="31"/>
       <c r="D8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E8" s="25"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G8" s="25"/>
+      <c r="G8" s="31"/>
       <c r="H8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I8" s="25"/>
+      <c r="I8" s="31"/>
       <c r="J8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">南</t>
         </is>
       </c>
-      <c r="K8" s="25"/>
+      <c r="K8" s="31"/>
       <c r="L8" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M8" s="25"/>
+      <c r="M8" s="31"/>
     </row>
     <row r="9" ht="55.19" customHeight="1">
       <c r="A9" s="0"/>
@@ -4103,41 +4126,41 @@
 –</t>
         </is>
       </c>
-      <c r="C9" s="25"/>
+      <c r="C9" s="31"/>
       <c r="D9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E9" s="25"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 姑</t>
         </is>
       </c>
-      <c r="G9" s="25"/>
+      <c r="G9" s="31"/>
       <c r="H9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="I9" s="25"/>
+      <c r="I9" s="31"/>
       <c r="J9" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –</t>
         </is>
       </c>
-      <c r="K9" s="25"/>
+      <c r="K9" s="31"/>
       <c r="L9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌
 汰</t>
         </is>
       </c>
-      <c r="M9" s="26"/>
+      <c r="M9" s="32"/>
     </row>
     <row r="10" ht="55.19" customHeight="1">
       <c r="A10" s="0"/>
@@ -4146,37 +4169,37 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C10" s="27"/>
+      <c r="C10" s="33"/>
       <c r="D10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E10" s="27"/>
+      <c r="E10" s="33"/>
       <c r="F10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="G10" s="27"/>
+      <c r="G10" s="33"/>
       <c r="H10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I10" s="27"/>
+      <c r="I10" s="33"/>
       <c r="J10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K10" s="27"/>
+      <c r="K10" s="33"/>
       <c r="L10" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">㴌</t>
         </is>
       </c>
-      <c r="M10" s="27"/>
+      <c r="M10" s="33"/>
     </row>
     <row r="11" ht="55.19" customHeight="1">
       <c r="A11" s="0"/>
@@ -4185,40 +4208,40 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C11" s="24"/>
+      <c r="C11" s="30"/>
       <c r="D11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="E11" s="24"/>
+      <c r="E11" s="30"/>
       <c r="F11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="G11" s="24"/>
+      <c r="G11" s="30"/>
       <c r="H11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
 潢</t>
         </is>
       </c>
-      <c r="I11" s="24"/>
+      <c r="I11" s="30"/>
       <c r="J11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢潢</t>
         </is>
       </c>
-      <c r="K11" s="24"/>
+      <c r="K11" s="30"/>
       <c r="L11" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="M11" s="24"/>
+      <c r="M11" s="30"/>
     </row>
     <row r="12" ht="55.19" customHeight="1">
       <c r="A12" s="0"/>
@@ -4227,37 +4250,37 @@
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="C12" s="25"/>
+      <c r="C12" s="31"/>
       <c r="D12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無</t>
         </is>
       </c>
-      <c r="E12" s="25"/>
+      <c r="E12" s="31"/>
       <c r="F12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="G12" s="25"/>
+      <c r="G12" s="31"/>
       <c r="H12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I12" s="25"/>
+      <c r="I12" s="31"/>
       <c r="J12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰無</t>
         </is>
       </c>
-      <c r="K12" s="25"/>
+      <c r="K12" s="31"/>
       <c r="L12" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M12" s="25"/>
+      <c r="M12" s="31"/>
     </row>
     <row r="13" ht="55.19" customHeight="1">
       <c r="A13" s="0"/>
@@ -4266,40 +4289,40 @@
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="C13" s="25"/>
+      <c r="C13" s="31"/>
       <c r="D13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="E13" s="25"/>
+      <c r="E13" s="31"/>
       <c r="F13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 –</t>
         </is>
       </c>
-      <c r="G13" s="25"/>
+      <c r="G13" s="31"/>
       <c r="H13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I13" s="25"/>
+      <c r="I13" s="31"/>
       <c r="J13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 無</t>
         </is>
       </c>
-      <c r="K13" s="25"/>
+      <c r="K13" s="31"/>
       <c r="L13" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 汰</t>
         </is>
       </c>
-      <c r="M13" s="25"/>
+      <c r="M13" s="31"/>
     </row>
     <row r="14" ht="55.19" customHeight="1">
       <c r="A14" s="0"/>
@@ -4308,33 +4331,33 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C14" s="27"/>
+      <c r="C14" s="33"/>
       <c r="D14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="E14" s="27"/>
+      <c r="E14" s="33"/>
       <c r="F14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="G14" s="27"/>
+      <c r="G14" s="33"/>
       <c r="H14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I14" s="27"/>
+      <c r="I14" s="33"/>
       <c r="J14" s="23"/>
-      <c r="K14" s="27"/>
+      <c r="K14" s="33"/>
       <c r="L14" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M14" s="27"/>
+      <c r="M14" s="33"/>
     </row>
     <row r="15" ht="55.19" customHeight="1">
       <c r="A15" s="0"/>
@@ -4343,39 +4366,39 @@
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="C15" s="24"/>
+      <c r="C15" s="30"/>
       <c r="D15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="E15" s="24"/>
+      <c r="E15" s="30"/>
       <c r="F15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="G15" s="24"/>
+      <c r="G15" s="30"/>
       <c r="H15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I15" s="24"/>
+      <c r="I15" s="30"/>
       <c r="J15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰
 湳</t>
         </is>
       </c>
-      <c r="K15" s="24"/>
+      <c r="K15" s="30"/>
       <c r="L15" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢
 汰</t>
         </is>
       </c>
-      <c r="M15" s="24"/>
+      <c r="M15" s="30"/>
     </row>
     <row r="16" ht="55.19" customHeight="1">
       <c r="A16" s="0"/>
@@ -4384,110 +4407,110 @@
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="C16" s="25"/>
+      <c r="C16" s="31"/>
       <c r="D16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢</t>
         </is>
       </c>
-      <c r="E16" s="25"/>
+      <c r="E16" s="31"/>
       <c r="F16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G16" s="25"/>
+      <c r="G16" s="31"/>
       <c r="H16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I16" s="25"/>
+      <c r="I16" s="31"/>
       <c r="J16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">潢汰</t>
         </is>
       </c>
-      <c r="K16" s="25"/>
+      <c r="K16" s="31"/>
       <c r="L16" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">汰</t>
         </is>
       </c>
-      <c r="M16" s="25"/>
+      <c r="M16" s="31"/>
     </row>
     <row r="17" ht="55.19" customHeight="1">
       <c r="A17" s="0"/>
       <c r="B17" s="23"/>
-      <c r="C17" s="25"/>
+      <c r="C17" s="31"/>
       <c r="D17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑
 –</t>
         </is>
       </c>
-      <c r="E17" s="25"/>
+      <c r="E17" s="31"/>
       <c r="F17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑姑</t>
         </is>
       </c>
-      <c r="G17" s="25"/>
+      <c r="G17" s="31"/>
       <c r="H17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="I17" s="25"/>
+      <c r="I17" s="31"/>
       <c r="J17" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">黃無
 –</t>
         </is>
       </c>
-      <c r="K17" s="25"/>
+      <c r="K17" s="31"/>
       <c r="L17" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">汰
 –</t>
         </is>
       </c>
-      <c r="M17" s="26"/>
+      <c r="M17" s="32"/>
     </row>
     <row r="18" ht="55.19" customHeight="1">
       <c r="A18" s="0"/>
       <c r="B18" s="23"/>
-      <c r="C18" s="27"/>
+      <c r="C18" s="33"/>
       <c r="D18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="E18" s="27"/>
+      <c r="E18" s="33"/>
       <c r="F18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">姑</t>
         </is>
       </c>
-      <c r="G18" s="27"/>
+      <c r="G18" s="33"/>
       <c r="H18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="I18" s="27"/>
+      <c r="I18" s="33"/>
       <c r="J18" s="23" t="inlineStr">
         <is>
           <t xml:space="preserve">–</t>
         </is>
       </c>
-      <c r="K18" s="27"/>
+      <c r="K18" s="33"/>
       <c r="L18" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">△</t>
         </is>
       </c>
-      <c r="M18" s="28"/>
+      <c r="M18" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -150,7 +150,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -233,6 +233,9 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -339,7 +342,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">5</t>
+          <t xml:space="preserve">7</t>
         </is>
       </c>
     </row>
@@ -399,7 +402,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡.</t>
+          <t xml:space="preserve">10-13 전면 재판독. 16정간 인쇄 양식(번호 1~16)이지만 가로선이 번호 2개마다만 있어 한 줄에 큰 칸 8개, 칸마다 율명 2~3개 → 큰 칸 1개 = 정간 1개(율명 위→아래 | ), 8정간 4/4. 오른쪽부터 6줄 사용, 7·8줄 빈 칸. 가사는 각 율명 줄 오른쪽 칸(줄1 정간5~6 가사는 오른쪽 여백). 칸 위·아래 붙임줄(호) 표시는 생략, 경계 &lt; 는 ‹. 한 곡. 10-15 潢/㴌 재대조.</t>
         </is>
       </c>
     </row>
@@ -907,14 +910,14 @@
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|–|姑</t>
+          <t xml:space="preserve">姑|–|南</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
-姑</t>
+南</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -993,14 +996,14 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">潢無|姑|姑</t>
+          <t xml:space="preserve">潢無|南|南</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
-姑
-姑</t>
+南
+南</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
@@ -1032,24 +1035,28 @@
       <c r="F13" s="2">
         <v>1</v>
       </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑|–|△</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
+      <c r="G13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南|–|△</t>
+        </is>
+      </c>
+      <c r="H13" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
 –
 △</t>
         </is>
       </c>
-      <c r="I13" s="2" t="inlineStr">
+      <c r="I13" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
       </c>
-      <c r="J13" s="4"/>
+      <c r="J13" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南/姑?</t>
+        </is>
+      </c>
       <c r="K13" s="2"/>
     </row>
     <row r="14">
@@ -1321,14 +1328,14 @@
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑|姑</t>
+          <t xml:space="preserve">南|南|南</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑
-姑</t>
+南
+南</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
@@ -1403,12 +1410,12 @@
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌姑|湳|–</t>
+          <t xml:space="preserve">㴌南|湳|–</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌姑
+          <t xml:space="preserve">㴌南
 湳
 –</t>
         </is>
@@ -1549,14 +1556,14 @@
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">湳|–|㴌</t>
+          <t xml:space="preserve">湳|–|潢</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">湳
 –
-㴌</t>
+潢</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -1588,24 +1595,27 @@
       <c r="F27" s="2">
         <v>1</v>
       </c>
-      <c r="G27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌|–|潢無</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-–
-潢無</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="inlineStr">
+      <c r="G27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳|–</t>
+        </is>
+      </c>
+      <c r="H27" s="3" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–</t>
+        </is>
+      </c>
+      <c r="I27" s="3" t="inlineStr">
         <is>
           <t xml:space="preserve">지고</t>
         </is>
       </c>
-      <c r="J27" s="4"/>
+      <c r="J27" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳 한 글자 길게(湳湳?)</t>
+        </is>
+      </c>
       <c r="K27" s="2"/>
     </row>
     <row r="28">
@@ -1787,14 +1797,14 @@
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">南|姑|姑</t>
+          <t xml:space="preserve">南|南|南</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑
-姑</t>
+南
+南</t>
         </is>
       </c>
       <c r="I32" s="2" t="inlineStr">
@@ -2080,13 +2090,13 @@
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑|–</t>
+          <t xml:space="preserve">南|南|–</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑
+          <t xml:space="preserve">南
+南
 –</t>
         </is>
       </c>
@@ -2162,13 +2172,13 @@
       </c>
       <c r="G41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑|姑|–</t>
+          <t xml:space="preserve">南南|南|–</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑
-姑
+          <t xml:space="preserve">南南
+南
 –</t>
         </is>
       </c>
@@ -2330,14 +2340,14 @@
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|–|姑</t>
+          <t xml:space="preserve">姑|–|南</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
           <t xml:space="preserve">姑
 –
-姑</t>
+南</t>
         </is>
       </c>
       <c r="I45" s="2" t="inlineStr">
@@ -2371,12 +2381,12 @@
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|–|潢無</t>
+          <t xml:space="preserve">南|–|潢無</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
+          <t xml:space="preserve">南
 –
 潢無</t>
         </is>
@@ -2412,14 +2422,14 @@
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|姑|姑</t>
+          <t xml:space="preserve">南|南|南</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑
-姑</t>
+          <t xml:space="preserve">南
+南
+南</t>
         </is>
       </c>
       <c r="I47" s="2" t="inlineStr">
@@ -2453,12 +2463,12 @@
       </c>
       <c r="G48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑|–|–</t>
+          <t xml:space="preserve">南|–|–</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
+          <t xml:space="preserve">南
 –
 –</t>
         </is>
@@ -2549,7 +2559,7 @@
         <is>
           <t xml:space="preserve">湳
 –
-㴌</t>
+潢</t>
         </is>
       </c>
       <c r="G3" s="22" t="inlineStr">
@@ -2575,7 +2585,7 @@
         <is>
           <t xml:space="preserve">姑
 –
-姑</t>
+南</t>
         </is>
       </c>
       <c r="K3" s="22" t="inlineStr">
@@ -2626,14 +2636,13 @@
 님</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">㴌
-–
-潢無</t>
-        </is>
-      </c>
-      <c r="G4" s="26" t="inlineStr">
+      <c r="F4" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">湳
+–</t>
+        </is>
+      </c>
+      <c r="G4" s="25" t="inlineStr">
         <is>
           <t xml:space="preserve">지
 고</t>
@@ -2717,8 +2726,8 @@
       <c r="H5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑
-姑</t>
+南
+南</t>
         </is>
       </c>
       <c r="I5" s="26" t="inlineStr">
@@ -2732,8 +2741,8 @@
       <c r="J5" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">潢無
-姑
-姑</t>
+南
+南</t>
         </is>
       </c>
       <c r="K5" s="26" t="inlineStr">
@@ -2764,7 +2773,7 @@
         <is>
           <t xml:space="preserve">姑
 –
-姑</t>
+南</t>
         </is>
       </c>
       <c r="C6" s="27" t="inlineStr">
@@ -2806,14 +2815,14 @@
           <t xml:space="preserve">나</t>
         </is>
       </c>
-      <c r="J6" s="21" t="inlineStr">
-        <is>
-          <t xml:space="preserve">姑
+      <c r="J6" s="23" t="inlineStr">
+        <is>
+          <t xml:space="preserve">南
 –
 △</t>
         </is>
       </c>
-      <c r="K6" s="27" t="inlineStr">
+      <c r="K6" s="28" t="inlineStr">
         <is>
           <t xml:space="preserve">요</t>
         </is>
@@ -2831,7 +2840,7 @@
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
+          <t xml:space="preserve">南
 –
 潢無</t>
         </is>
@@ -2870,7 +2879,7 @@
       </c>
       <c r="H7" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">㴌姑
+          <t xml:space="preserve">㴌南
 湳
 –</t>
         </is>
@@ -2912,9 +2921,9 @@
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑
-姑</t>
+          <t xml:space="preserve">南
+南
+南</t>
         </is>
       </c>
       <c r="C8" s="26" t="inlineStr">
@@ -2926,8 +2935,8 @@
       </c>
       <c r="D8" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
-姑
+          <t xml:space="preserve">南
+南
 –</t>
         </is>
       </c>
@@ -2987,7 +2996,7 @@
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑
+          <t xml:space="preserve">南
 –
 –</t>
         </is>
@@ -3013,8 +3022,8 @@
       <c r="F9" s="21" t="inlineStr">
         <is>
           <t xml:space="preserve">南
-姑
-姑</t>
+南
+南</t>
         </is>
       </c>
       <c r="G9" s="26" t="inlineStr">
@@ -3059,8 +3068,8 @@
       <c r="C10" s="27"/>
       <c r="D10" s="21" t="inlineStr">
         <is>
-          <t xml:space="preserve">姑姑
-姑
+          <t xml:space="preserve">南南
+南
 –</t>
         </is>
       </c>

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -65,10 +65,7 @@
       </patternFill>
     </fill>
     <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="solid">

--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -2485,6 +2485,9 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <pageSetUpPr fitToPage="0"/>
+  </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
@@ -2501,10 +2504,10 @@
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="77.61" customHeight="1">
+    <row r="2" ht="51.95" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2523,7 +2526,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="77.61" customHeight="1">
+    <row r="3" ht="115.86" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2604,7 +2607,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="77.61" customHeight="1">
+    <row r="4" ht="115.86" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2684,7 +2687,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="77.61" customHeight="1">
+    <row r="5" ht="115.86" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2764,7 +2767,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="77.61" customHeight="1">
+    <row r="6" ht="115.86" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2833,7 +2836,7 @@
       </c>
       <c r="M6" s="27"/>
     </row>
-    <row r="7" ht="77.61" customHeight="1">
+    <row r="7" ht="115.86" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2914,7 +2917,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="77.61" customHeight="1">
+    <row r="8" ht="115.86" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2989,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="77.61" customHeight="1">
+    <row r="9" ht="115.86" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3059,7 +3062,7 @@
       </c>
       <c r="M9" s="26"/>
     </row>
-    <row r="10" ht="77.61" customHeight="1">
+    <row r="10" ht="115.86" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="27"/>
@@ -3120,6 +3123,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="100"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
 </worksheet>
 </file>
--- a/sheets/민요/검수/신 만고강산.xlsx
+++ b/sheets/민요/검수/신 만고강산.xlsx
@@ -2490,24 +2490,24 @@
   </sheetPr>
   <cols>
     <col min="1" max="1" width="2" customWidth="1"/>
-    <col min="2" max="2" width="12" customWidth="1"/>
+    <col min="2" max="2" width="10.71" customWidth="1"/>
     <col min="3" max="3" width="6" customWidth="1"/>
-    <col min="4" max="4" width="12" customWidth="1"/>
+    <col min="4" max="4" width="10.71" customWidth="1"/>
     <col min="5" max="5" width="6" customWidth="1"/>
-    <col min="6" max="6" width="12" customWidth="1"/>
+    <col min="6" max="6" width="10.71" customWidth="1"/>
     <col min="7" max="7" width="6" customWidth="1"/>
-    <col min="8" max="8" width="12" customWidth="1"/>
+    <col min="8" max="8" width="10.71" customWidth="1"/>
     <col min="9" max="9" width="6" customWidth="1"/>
-    <col min="10" max="10" width="12" customWidth="1"/>
+    <col min="10" max="10" width="10.71" customWidth="1"/>
     <col min="11" max="11" width="6" customWidth="1"/>
-    <col min="12" max="12" width="12" customWidth="1"/>
+    <col min="12" max="12" width="10.71" customWidth="1"/>
     <col min="13" max="13" width="6" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" ht="6.0" customHeight="true">
       <c r="A1" s="0"/>
     </row>
-    <row r="2" ht="51.95" customHeight="true">
+    <row r="2" ht="48.19" customHeight="true">
       <c r="A2" s="0"/>
       <c r="B2" s="20" t="inlineStr">
         <is>
@@ -2526,7 +2526,7 @@
       <c r="L2" s="20"/>
       <c r="M2" s="20"/>
     </row>
-    <row r="3" ht="115.86" customHeight="true">
+    <row r="3" ht="107.43" customHeight="true">
       <c r="A3" s="0"/>
       <c r="B3" s="21" t="inlineStr">
         <is>
@@ -2607,7 +2607,7 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="115.86" customHeight="true">
+    <row r="4" ht="107.43" customHeight="true">
       <c r="A4" s="0"/>
       <c r="B4" s="23" t="inlineStr">
         <is>
@@ -2687,7 +2687,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="115.86" customHeight="true">
+    <row r="5" ht="107.43" customHeight="true">
       <c r="A5" s="0"/>
       <c r="B5" s="21" t="inlineStr">
         <is>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="115.86" customHeight="true">
+    <row r="6" ht="107.43" customHeight="true">
       <c r="A6" s="0"/>
       <c r="B6" s="21" t="inlineStr">
         <is>
@@ -2836,7 +2836,7 @@
       </c>
       <c r="M6" s="27"/>
     </row>
-    <row r="7" ht="115.86" customHeight="true">
+    <row r="7" ht="107.43" customHeight="true">
       <c r="A7" s="0"/>
       <c r="B7" s="21" t="inlineStr">
         <is>
@@ -2917,7 +2917,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="115.86" customHeight="true">
+    <row r="8" ht="107.43" customHeight="true">
       <c r="A8" s="0"/>
       <c r="B8" s="21" t="inlineStr">
         <is>
@@ -2992,7 +2992,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="115.86" customHeight="true">
+    <row r="9" ht="107.43" customHeight="true">
       <c r="A9" s="0"/>
       <c r="B9" s="21" t="inlineStr">
         <is>
@@ -3062,7 +3062,7 @@
       </c>
       <c r="M9" s="26"/>
     </row>
-    <row r="10" ht="115.86" customHeight="true">
+    <row r="10" ht="107.43" customHeight="true">
       <c r="A10" s="0"/>
       <c r="B10" s="21"/>
       <c r="C10" s="27"/>
@@ -3123,6 +3123,6 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.4" right="0.4" top="0.5" bottom="0.5" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" scale="77"/>
+  <pageSetup paperSize="9" orientation="portrait" scale="83"/>
 </worksheet>
 </file>